--- a/jogos_2025-04-02.xlsx
+++ b/jogos_2025-04-02.xlsx
@@ -901,22 +901,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>Tokyo Verdy</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.62</v>
+        <v>2.17</v>
       </c>
       <c r="M4" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O4" t="n">
         <v>3.1</v>
       </c>
-      <c r="N4" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="O4" t="n">
-        <v>3.4</v>
-      </c>
       <c r="P4" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="S4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>['20', '52']</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>['43', '89']</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>2.63</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X4" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>['90+8']</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>['12']</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>2.1</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45749.29166666666</v>
@@ -1030,25 +1030,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Yokohama F. Marinos</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.55</v>
+        <v>2.16</v>
       </c>
       <c r="M5" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="N5" t="n">
-        <v>2.64</v>
+        <v>3.31</v>
       </c>
       <c r="O5" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="P5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y5" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AC5" t="n">
         <v>1.95</v>
       </c>
-      <c r="Z5" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC5" t="n">
+      <c r="AD5" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD5" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['51', '84']</t>
+          <t>['3', '45+3']</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['44']</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.49</v>
+        <v>1.66</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45749.29166666666</v>
@@ -1159,25 +1159,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.16</v>
+        <v>1.9</v>
       </c>
       <c r="M6" t="n">
-        <v>3.27</v>
+        <v>3.67</v>
       </c>
       <c r="N6" t="n">
-        <v>3.31</v>
+        <v>3.67</v>
       </c>
       <c r="O6" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="P6" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Q6" t="n">
         <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>['50', '90+2']</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>2.5</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>['3', '45+3']</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>['44']</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>2.4</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45749.29166666666</v>
@@ -1288,25 +1288,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.9</v>
+        <v>3.12</v>
       </c>
       <c r="M7" t="n">
-        <v>3.67</v>
+        <v>3.04</v>
       </c>
       <c r="N7" t="n">
-        <v>3.67</v>
+        <v>2.38</v>
       </c>
       <c r="O7" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="P7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S7" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q7" t="n">
-        <v>4</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.25</v>
-      </c>
       <c r="T7" t="n">
-        <v>2.63</v>
+        <v>3.75</v>
       </c>
       <c r="U7" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="V7" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="W7" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="X7" t="n">
-        <v>3.95</v>
+        <v>2.55</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.67</v>
+        <v>2.37</v>
       </c>
       <c r="Z7" t="n">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.8</v>
+        <v>4.75</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.42</v>
+        <v>1.18</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>['50', '90+2']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['43']</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.27</v>
+        <v>1.55</v>
       </c>
       <c r="AH7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>2.5</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45749.29166666666</v>
@@ -1417,25 +1417,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.12</v>
+        <v>1.82</v>
       </c>
       <c r="M8" t="n">
-        <v>3.04</v>
+        <v>3.63</v>
       </c>
       <c r="N8" t="n">
-        <v>2.38</v>
+        <v>4.1</v>
       </c>
       <c r="O8" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="P8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y8" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U8" t="n">
+      <c r="Z8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB8" t="n">
         <v>1.25</v>
       </c>
-      <c r="V8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AC8" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
+          <t>['22']</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>['43']</t>
-        </is>
-      </c>
       <c r="AG8" t="n">
-        <v>1.55</v>
+        <v>1.22</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.35</v>
+        <v>1.9</v>
       </c>
       <c r="AI8" t="n">
-        <v>2.38</v>
+        <v>1.53</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.83</v>
+        <v>2.75</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45749.29166666666</v>
@@ -1546,22 +1546,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.82</v>
+        <v>2.31</v>
       </c>
       <c r="M9" t="n">
-        <v>3.63</v>
+        <v>3.08</v>
       </c>
       <c r="N9" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="O9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>['60']</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>2.5</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>['22']</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>2.75</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45749.29166666666</v>
@@ -1675,16 +1675,16 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
@@ -1693,7 +1693,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.47</v>
+        <v>2.62</v>
       </c>
       <c r="M10" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>2.27</v>
+        <v>2.74</v>
       </c>
       <c r="O10" t="n">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="P10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X10" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>['90+8']</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>['12']</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI10" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC10" t="n">
+      <c r="AJ10" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>['74']</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.73</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45749.29166666666</v>
@@ -1804,19 +1804,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>Yokohama F. Marinos</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.31</v>
+        <v>2.55</v>
       </c>
       <c r="M11" t="n">
-        <v>3.08</v>
+        <v>3.34</v>
       </c>
       <c r="N11" t="n">
-        <v>3.2</v>
+        <v>2.64</v>
       </c>
       <c r="O11" t="n">
         <v>3.2</v>
       </c>
       <c r="P11" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="S11" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="T11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U11" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="V11" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="W11" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="X11" t="n">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.63</v>
+        <v>1.95</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.45</v>
+        <v>1.79</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.25</v>
+        <v>3.45</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
+          <t>['51', '84']</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>['60']</t>
-        </is>
-      </c>
       <c r="AG11" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45749.29166666666</v>
@@ -1933,25 +1933,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tokyo Verdy</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.17</v>
+        <v>3.47</v>
       </c>
       <c r="M12" t="n">
-        <v>3.09</v>
+        <v>2.94</v>
       </c>
       <c r="N12" t="n">
-        <v>3.5</v>
+        <v>2.27</v>
       </c>
       <c r="O12" t="n">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="P12" t="n">
         <v>1.91</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="R12" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="S12" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="T12" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="U12" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V12" t="n">
         <v>1.1</v>
       </c>
       <c r="W12" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="X12" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.43</v>
+        <v>2.57</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['20', '52']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['43', '89']</t>
+          <t>['74']</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.32</v>
+        <v>1.61</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.58</v>
+        <v>1.3</v>
       </c>
       <c r="AI12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AJ12" t="n">
         <v>1.73</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>2.63</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45749.29166666666</v>
@@ -2181,26 +2181,26 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Khon Kaen United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
         <v>1</v>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="N14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O14" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AA14" t="n">
         <v>2.25</v>
       </c>
-      <c r="O14" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3</v>
-      </c>
-      <c r="R14" t="n">
+      <c r="AB14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>['52', '64']</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>['4']</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>1.44</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>['64']</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>['32']</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.8</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45749.33333333334</v>
@@ -2310,32 +2310,32 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="M15" t="n">
-        <v>3.37</v>
+        <v>3.5</v>
       </c>
       <c r="N15" t="n">
-        <v>2.58</v>
+        <v>2.25</v>
       </c>
       <c r="O15" t="n">
-        <v>3.44</v>
+        <v>3.75</v>
       </c>
       <c r="P15" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.34</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="T15" t="n">
-        <v>2.58</v>
+        <v>3.25</v>
       </c>
       <c r="U15" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W15" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="X15" t="n">
-        <v>3.58</v>
+        <v>3.25</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="AA15" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.56</v>
+        <v>1.91</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.21</v>
+        <v>1.91</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['13']</t>
+          <t>['64']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>['11', '70']</t>
+          <t>['32']</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.38</v>
+        <v>1.65</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45749.33333333334</v>
@@ -2449,22 +2449,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Khon Kaen United</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
         <v>2</v>
       </c>
-      <c r="H16" t="n">
-        <v>1</v>
-      </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
       <c r="M16" t="n">
-        <v>4.75</v>
+        <v>3.37</v>
       </c>
       <c r="N16" t="n">
-        <v>1.55</v>
+        <v>2.58</v>
       </c>
       <c r="O16" t="n">
-        <v>4.95</v>
+        <v>3.44</v>
       </c>
       <c r="P16" t="n">
-        <v>2.48</v>
+        <v>1.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.95</v>
+        <v>3.34</v>
       </c>
       <c r="R16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W16" t="n">
         <v>1.21</v>
       </c>
-      <c r="S16" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.14</v>
-      </c>
       <c r="X16" t="n">
-        <v>5.3</v>
+        <v>3.58</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.34</v>
+        <v>1.89</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.53</v>
+        <v>1.29</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.32</v>
+        <v>2.21</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['52', '64']</t>
+          <t>['13']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['4']</t>
+          <t>['11', '70']</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>2.36</v>
+        <v>1.38</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.1</v>
+        <v>1.36</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.68</v>
+        <v>2.02</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.44</v>
+        <v>2</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45749.33333333334</v>
@@ -2707,25 +2707,25 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.41</v>
+        <v>2.78</v>
       </c>
       <c r="M18" t="n">
-        <v>3.43</v>
+        <v>3.47</v>
       </c>
       <c r="N18" t="n">
-        <v>2.79</v>
+        <v>2.37</v>
       </c>
       <c r="O18" t="n">
-        <v>2.9</v>
+        <v>3.42</v>
       </c>
       <c r="P18" t="n">
-        <v>2.19</v>
+        <v>2.03</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="R18" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="S18" t="n">
-        <v>3.1</v>
+        <v>2.77</v>
       </c>
       <c r="T18" t="n">
-        <v>2.57</v>
+        <v>2.65</v>
       </c>
       <c r="U18" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="V18" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="W18" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="X18" t="n">
-        <v>3.93</v>
+        <v>3.69</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.74</v>
+        <v>1.87</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.03</v>
+        <v>1.87</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.76</v>
+        <v>2.94</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['71', '78']</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>['5', '45+3', '68']</t>
+          <t>['27', '90+1']</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.86</v>
+        <v>2.07</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45749.35763888889</v>
@@ -2836,109 +2836,109 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
         <v>2</v>
       </c>
-      <c r="H19" t="n">
-        <v>2</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.78</v>
+        <v>2.41</v>
       </c>
       <c r="M19" t="n">
-        <v>3.47</v>
+        <v>3.43</v>
       </c>
       <c r="N19" t="n">
-        <v>2.37</v>
+        <v>2.79</v>
       </c>
       <c r="O19" t="n">
-        <v>3.42</v>
+        <v>2.9</v>
       </c>
       <c r="P19" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X19" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Z19" t="n">
         <v>2.03</v>
       </c>
-      <c r="Q19" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X19" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AA19" t="n">
-        <v>2.94</v>
+        <v>2.76</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>['71', '78']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>['27', '90+1']</t>
+          <t>['5', '45+3', '68']</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="AI19" t="n">
-        <v>2.07</v>
+        <v>1.86</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45749.35763888889</v>
@@ -3094,25 +3094,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G21" t="n">
         <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
         <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.08</v>
+        <v>2.8</v>
       </c>
       <c r="M21" t="n">
-        <v>3.06</v>
+        <v>2.9</v>
       </c>
       <c r="N21" t="n">
-        <v>2.39</v>
+        <v>2.55</v>
       </c>
       <c r="O21" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P21" t="n">
         <v>1.95</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="R21" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>['31', '64']</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>['2']</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
         <v>1.44</v>
       </c>
-      <c r="S21" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>['13', '75']</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
+      <c r="AH21" t="n">
         <v>1.37</v>
       </c>
-      <c r="AH21" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AI21" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45749.41666666666</v>
@@ -3352,25 +3352,25 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3378,34 +3378,34 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.6</v>
+        <v>3.08</v>
       </c>
       <c r="M23" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T23" t="n">
         <v>3.1</v>
       </c>
-      <c r="N23" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="O23" t="n">
-        <v>4</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.3</v>
-      </c>
       <c r="U23" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="V23" t="n">
         <v>1.06</v>
@@ -3429,32 +3429,32 @@
         <v>1.2</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['14']</t>
+          <t>['13', '75']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>['44']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.67</v>
+        <v>1.37</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.63</v>
+        <v>1.91</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45749.41666666666</v>
@@ -3481,81 +3481,81 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="O24" t="n">
+        <v>4</v>
+      </c>
+      <c r="P24" t="n">
         <v>2</v>
       </c>
-      <c r="H24" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L24" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="M24" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N24" t="n">
+      <c r="Q24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S24" t="n">
         <v>2.55</v>
       </c>
-      <c r="O24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.47</v>
-      </c>
       <c r="T24" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U24" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V24" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W24" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="X24" t="n">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AA24" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AC24" t="n">
         <v>1.95</v>
@@ -3565,25 +3565,25 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>['31', '64']</t>
+          <t>['14']</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>['2']</t>
+          <t>['44']</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="AI24" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45749.41666666666</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,25 +4126,25 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G29" t="n">
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I29" t="n">
         <v>1</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="M29" t="n">
-        <v>3.6</v>
+        <v>3.23</v>
       </c>
       <c r="N29" t="n">
-        <v>1.52</v>
+        <v>2.77</v>
       </c>
       <c r="O29" t="n">
-        <v>6</v>
+        <v>3.25</v>
       </c>
       <c r="P29" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="R29" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="S29" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="T29" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="U29" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V29" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W29" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="X29" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="AB29" t="n">
         <v>1.22</v>
       </c>
       <c r="AC29" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>['7']</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>['16', '73']</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ29" t="n">
         <v>2.2</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>['37']</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>['47']</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>1.36</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45749.5625</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,25 +4255,25 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G30" t="n">
         <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
         <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -4281,83 +4281,83 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="M30" t="n">
-        <v>3.23</v>
+        <v>3.6</v>
       </c>
       <c r="N30" t="n">
-        <v>2.77</v>
+        <v>1.52</v>
       </c>
       <c r="O30" t="n">
-        <v>3.25</v>
+        <v>6</v>
       </c>
       <c r="P30" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="R30" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S30" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="T30" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="U30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W30" t="n">
         <v>1.3</v>
       </c>
-      <c r="V30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.38</v>
-      </c>
       <c r="X30" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="AB30" t="n">
         <v>1.22</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['7']</t>
+          <t>['37']</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>['16', '73']</t>
+          <t>['47']</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.45</v>
+        <v>2.4</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.4</v>
+        <v>1.07</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.91</v>
+        <v>3.75</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.2</v>
+        <v>1.36</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45749.5625</v>
@@ -4513,25 +4513,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H32" t="n">
         <v>2</v>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -4539,83 +4539,83 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.52</v>
+        <v>2.45</v>
       </c>
       <c r="M32" t="n">
-        <v>4.3</v>
+        <v>3.39</v>
       </c>
       <c r="N32" t="n">
-        <v>5.6</v>
+        <v>2.73</v>
       </c>
       <c r="O32" t="n">
-        <v>2.05</v>
+        <v>2.95</v>
       </c>
       <c r="P32" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="Q32" t="n">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="R32" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S32" t="n">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="T32" t="n">
         <v>2.5</v>
       </c>
       <c r="U32" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="V32" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W32" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="X32" t="n">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>['43']</t>
+          <t>['89', '90+5']</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>['80', '90+4']</t>
+          <t>['5', '74']</t>
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.14</v>
+        <v>1.43</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.37</v>
+        <v>1.52</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.36</v>
+        <v>1.9</v>
       </c>
       <c r="AJ32" t="n">
-        <v>3.2</v>
+        <v>2.05</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45749.64583333334</v>
@@ -4642,25 +4642,25 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33" t="n">
         <v>2</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -4668,83 +4668,83 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.45</v>
+        <v>1.52</v>
       </c>
       <c r="M33" t="n">
-        <v>3.39</v>
+        <v>4.3</v>
       </c>
       <c r="N33" t="n">
-        <v>2.73</v>
+        <v>5.6</v>
       </c>
       <c r="O33" t="n">
-        <v>2.95</v>
+        <v>2.05</v>
       </c>
       <c r="P33" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="R33" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S33" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="T33" t="n">
         <v>2.5</v>
       </c>
       <c r="U33" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="V33" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W33" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="X33" t="n">
-        <v>3.7</v>
+        <v>4.33</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>['89', '90+5']</t>
+          <t>['43']</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>['5', '74']</t>
+          <t>['80', '90+4']</t>
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.52</v>
+        <v>2.37</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.9</v>
+        <v>1.36</v>
       </c>
       <c r="AJ33" t="n">
-        <v>2.05</v>
+        <v>3.2</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45749.64583333334</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,22 +4771,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4797,28 +4797,28 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>5.4</v>
+        <v>1.65</v>
       </c>
       <c r="M34" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="N34" t="n">
-        <v>1.65</v>
+        <v>4.5</v>
       </c>
       <c r="O34" t="n">
-        <v>5.5</v>
+        <v>2.38</v>
       </c>
       <c r="P34" t="n">
         <v>2.3</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.2</v>
+        <v>4.5</v>
       </c>
       <c r="R34" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="T34" t="n">
         <v>2.63</v>
@@ -4827,53 +4827,53 @@
         <v>1.44</v>
       </c>
       <c r="V34" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W34" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X34" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Z34" t="n">
         <v>2.1</v>
       </c>
       <c r="AA34" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>['20']</t>
+          <t>['47', '54', '74']</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>['90+2']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.17</v>
+        <v>2.05</v>
       </c>
       <c r="AI34" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.4</v>
+        <v>2.63</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45749.65625</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,19 +4900,19 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.95</v>
+        <v>2.48</v>
       </c>
       <c r="M35" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="N35" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="O35" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q35" t="n">
         <v>4</v>
       </c>
-      <c r="N35" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O35" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="P35" t="n">
+      <c r="R35" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X35" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>['48', '52']</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ35" t="n">
         <v>2.4</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S35" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X35" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>['51', '78', '90+10']</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>2.3</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45749.65625</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,109 +5029,109 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>5</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>3</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
         <v>2</v>
       </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L36" t="n">
-        <v>2.48</v>
-      </c>
       <c r="M36" t="n">
-        <v>2.92</v>
+        <v>3.4</v>
       </c>
       <c r="N36" t="n">
-        <v>3.09</v>
+        <v>3.3</v>
       </c>
       <c r="O36" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q36" t="n">
         <v>3.25</v>
       </c>
-      <c r="P36" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>4</v>
-      </c>
       <c r="R36" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X36" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC36" t="n">
         <v>1.62</v>
       </c>
-      <c r="S36" t="n">
+      <c r="AD36" t="n">
         <v>2.2</v>
       </c>
-      <c r="T36" t="n">
-        <v>4</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X36" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC36" t="n">
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>['11', '23', '43', '57', '70']</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ36" t="n">
         <v>2.2</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>['48', '52']</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>2.4</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45749.65625</v>
@@ -5158,22 +5158,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G37" t="n">
         <v>2</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -5184,83 +5184,83 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.15</v>
+        <v>1.71</v>
       </c>
       <c r="M37" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="N37" t="n">
-        <v>14</v>
+        <v>4.1</v>
       </c>
       <c r="O37" t="n">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="P37" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="Q37" t="n">
-        <v>10</v>
+        <v>4.33</v>
       </c>
       <c r="R37" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="S37" t="n">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="T37" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="U37" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="V37" t="n">
         <v>1.01</v>
       </c>
       <c r="W37" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X37" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.2</v>
+        <v>2.74</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AB37" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>['2', '29']</t>
+          <t>['45+2', '74']</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['66']</t>
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="AH37" t="n">
-        <v>4.8</v>
+        <v>2.15</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="AJ37" t="n">
-        <v>4.75</v>
+        <v>2.5</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45749.65625</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,19 +5287,19 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G38" t="n">
         <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" t="n">
         <v>1</v>
@@ -5313,83 +5313,83 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.8</v>
+        <v>5.4</v>
       </c>
       <c r="M38" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="N38" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="O38" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X38" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD38" t="n">
         <v>1.95</v>
       </c>
-      <c r="O38" t="n">
-        <v>4</v>
-      </c>
-      <c r="P38" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T38" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X38" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>['45']</t>
+          <t>['20']</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+2']</t>
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.77</v>
+        <v>2.2</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AI38" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45749.65625</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,19 +5416,19 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>1</v>
@@ -5442,83 +5442,83 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.71</v>
+        <v>3.8</v>
       </c>
       <c r="M39" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="N39" t="n">
-        <v>4.1</v>
+        <v>1.95</v>
       </c>
       <c r="O39" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="P39" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.33</v>
+        <v>2.63</v>
       </c>
       <c r="R39" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X39" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB39" t="n">
         <v>1.25</v>
       </c>
-      <c r="S39" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X39" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AC39" t="n">
-        <v>1.5</v>
+        <v>1.91</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>['45+2', '74']</t>
+          <t>['45']</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>['66']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.21</v>
+        <v>1.77</v>
       </c>
       <c r="AH39" t="n">
-        <v>2.15</v>
+        <v>1.25</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="AJ39" t="n">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45749.65625</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,109 +5545,109 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" t="n">
+        <v>2</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M40" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N40" t="n">
+        <v>7</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P40" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>6</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X40" t="n">
         <v>5</v>
       </c>
-      <c r="I40" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" t="n">
-        <v>3</v>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L40" t="n">
-        <v>2</v>
-      </c>
-      <c r="M40" t="n">
+      <c r="Y40" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>['67']</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>['34', '60']</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AJ40" t="n">
         <v>3.4</v>
-      </c>
-      <c r="N40" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O40" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P40" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S40" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X40" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>['11', '23', '43', '57', '70']</t>
-        </is>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>2.2</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45749.65625</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,20 +5674,20 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
         <v>3</v>
       </c>
-      <c r="H41" t="n">
-        <v>0</v>
-      </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
@@ -5700,83 +5700,83 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="M41" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="N41" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="O41" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="P41" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S41" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X41" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>['51', '78', '90+10']</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ41" t="n">
         <v>2.3</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S41" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T41" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X41" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>['47', '54', '74']</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>2.63</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45749.65625</v>
@@ -5803,25 +5803,25 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
         <v>2</v>
       </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5829,83 +5829,83 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.4</v>
+        <v>1.15</v>
       </c>
       <c r="M42" t="n">
-        <v>4.9</v>
+        <v>9</v>
       </c>
       <c r="N42" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="O42" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="P42" t="n">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="Q42" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R42" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="S42" t="n">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="T42" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="U42" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="V42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X42" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>['2', '29']</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
         <v>1.03</v>
       </c>
-      <c r="W42" t="n">
+      <c r="AH42" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AI42" t="n">
         <v>1.17</v>
       </c>
-      <c r="X42" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>['67']</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>['34', '60']</t>
-        </is>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AJ42" t="n">
-        <v>3.4</v>
+        <v>4.75</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45749.65625</v>
@@ -6835,19 +6835,19 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Talleres Córdoba</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
@@ -6861,83 +6861,83 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.13</v>
+        <v>2.53</v>
       </c>
       <c r="M50" t="n">
-        <v>2.93</v>
+        <v>3.32</v>
       </c>
       <c r="N50" t="n">
-        <v>3.85</v>
+        <v>2.68</v>
       </c>
       <c r="O50" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P50" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S50" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T50" t="n">
         <v>3</v>
       </c>
-      <c r="P50" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R50" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S50" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T50" t="n">
-        <v>4</v>
-      </c>
       <c r="U50" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="V50" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="W50" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="X50" t="n">
-        <v>2.3</v>
+        <v>3.35</v>
       </c>
       <c r="Y50" t="n">
-        <v>2.67</v>
+        <v>1.92</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.44</v>
+        <v>1.82</v>
       </c>
       <c r="AA50" t="n">
-        <v>5.25</v>
+        <v>3.35</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AC50" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
+          <t>['59']</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF50" t="inlineStr">
-        <is>
-          <t>['76']</t>
-        </is>
-      </c>
       <c r="AG50" t="n">
-        <v>1.26</v>
+        <v>1.46</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.66</v>
+        <v>1.47</v>
       </c>
       <c r="AI50" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AJ50" t="n">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="AK50" s="3" t="n">
         <v>45749.89583333334</v>
@@ -6964,25 +6964,25 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Universitario</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>River Plate</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -6990,83 +6990,83 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.53</v>
+        <v>4.6</v>
       </c>
       <c r="M51" t="n">
-        <v>3.32</v>
+        <v>2.98</v>
       </c>
       <c r="N51" t="n">
-        <v>2.68</v>
+        <v>1.93</v>
       </c>
       <c r="O51" t="n">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
       <c r="P51" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.4</v>
+        <v>2.65</v>
       </c>
       <c r="R51" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="S51" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="T51" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U51" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="V51" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="W51" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="X51" t="n">
-        <v>3.35</v>
+        <v>2.37</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.92</v>
+        <v>2.28</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.82</v>
+        <v>1.63</v>
       </c>
       <c r="AA51" t="n">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AC51" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD51" t="n">
         <v>1.7</v>
       </c>
-      <c r="AD51" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>['59']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['17']</t>
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>1.46</v>
+        <v>1.73</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.47</v>
+        <v>1.24</v>
       </c>
       <c r="AI51" t="n">
-        <v>1.83</v>
+        <v>2.6</v>
       </c>
       <c r="AJ51" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AK51" s="3" t="n">
         <v>45749.89583333334</v>
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Universitario</t>
+          <t>Talleres Córdoba</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>River Plate</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7111,7 +7111,7 @@
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -7119,61 +7119,61 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>4.6</v>
+        <v>2.13</v>
       </c>
       <c r="M52" t="n">
-        <v>2.98</v>
+        <v>2.93</v>
       </c>
       <c r="N52" t="n">
-        <v>1.93</v>
+        <v>3.85</v>
       </c>
       <c r="O52" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="P52" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.65</v>
+        <v>4.5</v>
       </c>
       <c r="R52" t="n">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="S52" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="T52" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="U52" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="V52" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="W52" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X52" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.28</v>
+        <v>2.67</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AA52" t="n">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AC52" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7182,20 +7182,20 @@
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>['17']</t>
+          <t>['76']</t>
         </is>
       </c>
       <c r="AG52" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AI52" t="n">
         <v>1.73</v>
       </c>
-      <c r="AH52" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AJ52" t="n">
-        <v>1.73</v>
+        <v>2.63</v>
       </c>
       <c r="AK52" s="3" t="n">
         <v>45749.89583333334</v>
